--- a/changes/556-muzzles.xlsx
+++ b/changes/556-muzzles.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-dev\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BEE45D-D17D-412D-A2B6-E7E0916A5E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F3FE78-707E-47AB-A02B-C29F144128B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="31995" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="556 Muzzle Loudness Values" sheetId="1" r:id="rId1"/>
@@ -808,14 +808,14 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="K3">
         <v>500</v>
       </c>
       <c r="L3" s="1">
         <f>C3-D3*20-E3*0.8-F3*0.6-G3*10+H3*20+I3/200-J3*5</f>
-        <v>16.5</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="N3">
         <v>4.8</v>
@@ -861,14 +861,14 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="K4">
         <v>400</v>
       </c>
       <c r="L4" s="1">
         <f t="shared" ref="L4:L49" si="1">C4-D4*20-E4*0.8-F4*0.6-G4*10+H4*20+I4/200-J4*5</f>
-        <v>16.5</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="N4">
         <v>3.8</v>
@@ -1129,14 +1129,14 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0.09</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="K9">
         <v>700</v>
       </c>
       <c r="L9" s="1">
         <f t="shared" si="1"/>
-        <v>16.95</v>
+        <v>17.049999999999997</v>
       </c>
       <c r="N9">
         <v>3.9</v>
@@ -1290,14 +1290,14 @@
         <v>20</v>
       </c>
       <c r="J12">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="K12">
         <v>500</v>
       </c>
       <c r="L12" s="1">
         <f t="shared" si="1"/>
-        <v>14.85</v>
+        <v>15.049999999999999</v>
       </c>
       <c r="N12">
         <v>4.5999999999999996</v>
@@ -1718,14 +1718,14 @@
         <v>40</v>
       </c>
       <c r="J20">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="K20">
         <v>300</v>
       </c>
       <c r="L20" s="1">
         <f t="shared" si="1"/>
-        <v>16.05</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="N20">
         <v>7.2</v>
@@ -1979,14 +1979,14 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="K25">
         <v>500</v>
       </c>
       <c r="L25" s="1">
         <f t="shared" si="1"/>
-        <v>16.800000000000004</v>
+        <v>16.900000000000002</v>
       </c>
       <c r="N25">
         <v>3.84</v>
@@ -2136,14 +2136,14 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="K28">
         <v>500</v>
       </c>
       <c r="L28" s="1">
         <f t="shared" si="1"/>
-        <v>17.299999999999997</v>
+        <v>17.349999999999998</v>
       </c>
       <c r="N28">
         <v>4.8</v>
@@ -2291,14 +2291,14 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="K31">
         <v>600</v>
       </c>
       <c r="L31" s="1">
         <f t="shared" si="1"/>
-        <v>17.150000000000002</v>
+        <v>17.350000000000001</v>
       </c>
       <c r="N31">
         <v>3.8</v>
@@ -2344,14 +2344,14 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="K32">
         <v>500</v>
       </c>
       <c r="L32" s="1">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="N32">
         <v>3.6</v>
@@ -2630,14 +2630,14 @@
         <v>0</v>
       </c>
       <c r="J39">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="K39">
         <v>750</v>
       </c>
       <c r="L39" s="1">
         <f t="shared" si="1"/>
-        <v>16.5</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="O39">
         <f>N39*0.015</f>
@@ -2770,14 +2770,14 @@
         <v>80</v>
       </c>
       <c r="J43">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="K43">
         <v>600</v>
       </c>
       <c r="L43" s="1">
         <f t="shared" si="1"/>
-        <v>-7.5500000000000007</v>
+        <v>-7.3000000000000007</v>
       </c>
       <c r="O43">
         <f>N43*0.015</f>
@@ -2820,14 +2820,14 @@
         <v>40</v>
       </c>
       <c r="J44">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="K44">
         <v>500</v>
       </c>
       <c r="L44" s="1">
         <f t="shared" si="1"/>
-        <v>-4.2999999999999989</v>
+        <v>-4.1499999999999995</v>
       </c>
       <c r="O44">
         <f>N44*0.015</f>
@@ -2870,14 +2870,14 @@
         <v>20</v>
       </c>
       <c r="J45">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="K45">
         <v>400</v>
       </c>
       <c r="L45" s="1">
         <f t="shared" si="1"/>
-        <v>-2.2499999999999996</v>
+        <v>-2.1999999999999997</v>
       </c>
       <c r="O45">
         <f>N45*0.015</f>
